--- a/hira_material_automation/output/monthly/202601_202605__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__nonmetal_anchor__040019__normalized.xlsx
@@ -431,7 +431,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -486,7 +486,11 @@
           <t>040019</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>25898</t>
@@ -519,7 +523,11 @@
           <t>040019</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>25055</t>
@@ -552,7 +560,11 @@
           <t>040019</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>25458</t>
@@ -625,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-04T22:06:42</t>
+          <t>2026-05-14T22:14:55</t>
         </is>
       </c>
     </row>
@@ -637,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>820f06e43502b9430fa5fb182cfd8afc0169614dc13b617851498d6bb678e943</t>
+          <t>2f80e2d185da61878cbe51cbab9f5efcb26051b3a590ef2ccf1aa2eac05ba9f9</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202605__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__nonmetal_anchor__040019__normalized.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-14T22:14:55</t>
+          <t>2026-05-24T21:59:22</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2f80e2d185da61878cbe51cbab9f5efcb26051b3a590ef2ccf1aa2eac05ba9f9</t>
+          <t>bb31a0cf7439113df51d849969f54d464628a1e4ca8f6e520c7ce5f22e5d0da7</t>
         </is>
       </c>
     </row>
